--- a/WWW/data/Direcciones_corr.xlsx
+++ b/WWW/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE9831A-BCBD-418A-9F3B-1154A54CE59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B6B8A9-8811-462B-BD43-2F67099CAE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>

--- a/WWW/data/Direcciones_corr.xlsx
+++ b/WWW/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B6B8A9-8811-462B-BD43-2F67099CAE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE9831A-BCBD-418A-9F3B-1154A54CE59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
